--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +676,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Baseus Bowie MP1 หูฟัง True Wireless Bluetooth ไร้สาย</t>
@@ -741,7 +740,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>รองเท้าแมรี่เจน พื้นนุ่ม กันลื่น สไตล์มินิมอล</t>
@@ -800,7 +798,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Orsen by Eloop E29 แบตสำรอง 30000mAh QC3.0 PD 45W</t>
@@ -863,7 +860,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Gaabor หม้อทอดไร้น้ำมัน 4 ลิตร AF-35M รุ่น Official</t>
@@ -894,14 +890,8 @@
           <t>ลองเข้ามาดู ข้าวหมูทอดอร่อยมาก ที่ Shopee! https://spf.shopee.co.th/BQmRZCjn6</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>DHC วิตามินซี Zinc อาหารเสริมบำรุงผิว นำเข้าจากญี่ปุ่น</t>
@@ -932,14 +922,8 @@
           <t>ลองเข้ามาดู Chester's ที่ Shopee! https://spf.shopee.co.th/9pbHxIUZ3g</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>เครื่องให้อาหารสัตว์เลี้ยงอัตโนมัติ 4 ลิตร ตั้งเวลาผ่านมือถือ</t>
@@ -970,14 +954,8 @@
           <t>ลองเข้ามาดู McDonald's ที่ Shopee! https://spf.shopee.co.th/3B4O11yxCV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Baseus โคมไฟตั้งโต๊ะ LED แม่เหล็กไร้สาย Magnetic</t>
@@ -1008,14 +986,8 @@
           <t>ลองเข้ามาดู KFC ที่ Shopee! https://spf.shopee.co.th/6L1PmpO0Jy</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Rojeco เครื่องให้อาหารแมวอัตโนมัติ ปุ่มกด WIFI ควบคุมอัจฉริยะ ขนาด 2 ลิตร</t>
@@ -1046,14 +1018,8 @@
           <t>ลองเข้ามาดู Starbucks ที่ Shopee! https://spf.shopee.co.th/809dlpHQ2L</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Dr.Zkin Pet Spray ผลิตภัณฑ์สำหรับสัตว์เลี้ยง บำรุงขน ดับกลิ่น เพิ่มความหอม</t>
@@ -1084,14 +1050,8 @@
           <t>ลองเข้ามาดู Punthai Coffee ที่ Shopee! https://spf.shopee.co.th/7AaWmGyzrV</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช 15 ปี ตัวแป้งทำจากมันเทศ เก็บได้นานเดือน อุ่นเวฟทานได้เรื่อยๆ</t>
@@ -1122,14 +1082,8 @@
           <t>ลองเข้ามาดู ครัวฅนลาบ.ตำ.สั่ง  ที่ Shopee! https://spf.shopee.co.th/3qK4o80svV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>แคบหมูกึ่งสำเร็จรูป (ติดมัน) Pig a Pop แคบหมูแบบทอดเอง แคบหมูป๊อป แคบหมู แคปหมู</t>
@@ -1160,14 +1114,8 @@
           <t>ลองเข้ามาดู Café Amazon  ที่ Shopee! https://spf.shopee.co.th/40dV0P4yci</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>(ได้เยอะ จุใจ!! ) สาหร่ายทอดกรอบ กระป๋องใหญ่ 2700ml ปริมาณ145g มีให้เลือก3รส ดั้งเดิม ต้มยำ หม่าล่า</t>
@@ -1193,15 +1141,8 @@
           <t>ลด 20% วันนี้เท่านั้น</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>น้ำมันมรกต ขนาด 1 ลิตร สำหรับทำอาหาร แพ็ค 3 ขวด | น้ำมันพืชทำอาหาร ผัด ทอด อเนกประสงค์ ใช้ได้ทุกเมนู</t>
@@ -1227,15 +1168,8 @@
           <t>ลด 20% วันนี้เท่านั้น</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>[✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม] ปลากระป๋อง ตรา สามแม่ครัว ปลาแมคเคอเรลในซอสมะเขือเทศ 155 กรัม x 8 กระป๋อง ♥ ล็อตใหม่</t>
@@ -1261,15 +1195,8 @@
           <t>ลด 20% วันนี้เท่านั้น</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 5 กระปุก สุดฮิต แถมฟรีน้ำจิ้ม</t>
@@ -1295,15 +1222,8 @@
           <t>ลด 20% วันนี้เท่านั้น</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>yoyopet : Furry Fresh สเปรย์ปรับอากาศ สเปรย์น้ำหอม ดับกลิ่นฉี่แมวและสัตว์เลี้ยง ปลอดภัย 500ml</t>
@@ -1329,12 +1249,6 @@
           <t>ลด 20% วันนี้เท่านั้น</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1365,12 +1279,6 @@
           <t>สมาร์ททีวี 4K ภาพคมชัด ประกันศูนย์</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1401,12 +1309,6 @@
           <t>ทองคำแท้ 96.5% มีใบรับประกัน ออมทองมั่นใจ</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1437,12 +1339,6 @@
           <t>กางเกงในชาย GQ Cool Tech ไข่เย็น สวมสบาย ระบายอากาศได้ดี</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1473,12 +1369,6 @@
           <t>แชมพูปิดผมขาวหอมเกศ กลิ่นหอม บำรุงเส้นผมดกดำเป็นธรรมชาติ</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1509,12 +1399,6 @@
           <t>หมอนหนุนคุณภาพสูง TOTORI รุ่นคลาวด์ นุ่มสบาย รองรับสรีระได้ดี</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1530,7 +1414,6 @@
           <t>https://s.shopee.co.th/7VEfFsvKaC</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1541,12 +1424,6 @@
           <t>ราคาพิเศษเพียง 370 บาท | ขายได้ 117 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1562,7 +1439,6 @@
           <t>https://s.shopee.co.th/1BKbiFSaJe</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1573,12 +1449,6 @@
           <t>ราคาพิเศษเพียง 320 บาท | ขายได้ 76 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1594,7 +1464,6 @@
           <t>https://s.shopee.co.th/80AvqoGO9N</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1605,12 +1474,6 @@
           <t>ราคาพิเศษเพียง 39 บาท | ขายได้ 45 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1626,7 +1489,6 @@
           <t>https://s.shopee.co.th/30mFtchbVD</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1637,12 +1499,6 @@
           <t>ราคาพิเศษเพียง 323 บาท | ขายได้ 43 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1658,7 +1514,6 @@
           <t>https://s.shopee.co.th/2LWZ6OswQB</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1669,12 +1524,6 @@
           <t>ราคาพิเศษเพียง 690 บาท | ขายได้ 66 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1690,7 +1539,6 @@
           <t>https://s.shopee.co.th/9fJ9pseQfr</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1701,12 +1549,6 @@
           <t>ราคาพิเศษเพียง 85 บาท | ขายได้ 50 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1722,7 +1564,6 @@
           <t>https://s.shopee.co.th/7VEfFu4YGN</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1733,12 +1574,6 @@
           <t>ราคาพิเศษเพียง 328 บาท | ขายได้ 277 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1754,7 +1589,6 @@
           <t>https://s.shopee.co.th/1qaIVUhisT</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1765,12 +1599,6 @@
           <t>ราคาพิเศษเพียง 504 บาท | ขายได้ 37 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1786,7 +1614,6 @@
           <t>https://s.shopee.co.th/AUsGpQNn7J</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1797,12 +1624,6 @@
           <t>ราคาพิเศษเพียง 327 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1818,7 +1639,6 @@
           <t>https://s.shopee.co.th/20tihoBGes</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1829,12 +1649,6 @@
           <t>ราคาพิเศษเพียง 1020 บาท | ขายได้ 910 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1850,7 +1664,6 @@
           <t>https://s.shopee.co.th/70IOf0AS0z</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1861,12 +1674,6 @@
           <t>ราคาพิเศษเพียง 208 บาท | ขายได้ 31 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1882,7 +1689,6 @@
           <t>https://s.shopee.co.th/4fuTsiaeol</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1893,12 +1699,6 @@
           <t>ราคาพิเศษเพียง 257 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1914,7 +1714,6 @@
           <t>https://s.shopee.co.th/1VxS6u3tna</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1925,12 +1724,6 @@
           <t>ราคาพิเศษเพียง 175 บาท | ขายได้ 22 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1946,7 +1739,6 @@
           <t>https://s.shopee.co.th/qhlJgO6Xm</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1957,12 +1749,6 @@
           <t>ราคาพิเศษเพียง 756 บาท | ขายได้ 29 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1978,7 +1764,6 @@
           <t>https://s.shopee.co.th/AAFQQq6vcz</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1989,12 +1774,6 @@
           <t>ราคาพิเศษเพียง 251 บาท | ขายได้ 29 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2010,7 +1789,6 @@
           <t>https://s.shopee.co.th/1qaIVWus1e</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2021,12 +1799,6 @@
           <t>ราคาพิเศษเพียง 234 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2042,7 +1814,6 @@
           <t>https://s.shopee.co.th/9zw0EXbwrg</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2053,12 +1824,6 @@
           <t>ราคาพิเศษเพียง 262 บาท | ขายได้ 278 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2074,7 +1839,6 @@
           <t>https://s.shopee.co.th/8pk2qOxe3x</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2085,12 +1849,6 @@
           <t>ราคาพิเศษเพียง 487 บาท | ขายได้ 39 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2106,7 +1864,6 @@
           <t>https://s.shopee.co.th/qhlJhh5Rx</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2117,12 +1874,6 @@
           <t>ราคาพิเศษเพียง 304 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2138,7 +1889,6 @@
           <t>https://s.shopee.co.th/6VM847bfaQ</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2149,12 +1899,6 @@
           <t>ราคาพิเศษเพียง 693 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2170,7 +1914,6 @@
           <t>https://s.shopee.co.th/9AMtF2HyEz</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2181,12 +1924,6 @@
           <t>ราคาพิเศษเพียง 149 บาท | ขายได้ 43 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2202,7 +1939,6 @@
           <t>https://s.shopee.co.th/5VTasInfKp</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2213,12 +1949,6 @@
           <t>ราคาพิเศษเพียง 336 บาท | ขายได้ 27 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2234,7 +1964,6 @@
           <t>https://s.shopee.co.th/2VpzInGTld</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2245,12 +1974,6 @@
           <t>ราคาพิเศษเพียง 50 บาท | ขายได้ 21 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2266,7 +1989,6 @@
           <t>https://s.shopee.co.th/3g1wgxG6QW</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2277,12 +1999,6 @@
           <t>ราคาพิเศษเพียง 360 บาท | ขายได้ 19 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2298,7 +2014,6 @@
           <t>https://s.shopee.co.th/18eKDdCj1</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2309,12 +2024,6 @@
           <t>ราคาพิเศษเพียง 344 บาท | ขายได้ 15 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2330,7 +2039,6 @@
           <t>https://s.shopee.co.th/8fQce9KRPW</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2341,12 +2049,6 @@
           <t>ราคาพิเศษเพียง 341 บาท | ขายได้ 23 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2362,7 +2064,6 @@
           <t>https://s.shopee.co.th/40en5Znxih</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2373,12 +2074,6 @@
           <t>ราคาพิเศษเพียง 399 บาท | ขายได้ 15 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2394,7 +2089,6 @@
           <t>https://s.shopee.co.th/1BKbiNBwrB</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2405,12 +2099,6 @@
           <t>ราคาพิเศษเพียง 751 บาท | ขายได้ 21 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2426,7 +2114,6 @@
           <t>https://s.shopee.co.th/qhlJlVdlh</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2437,12 +2124,6 @@
           <t>ราคาพิเศษเพียง 1112 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2458,7 +2139,6 @@
           <t>https://s.shopee.co.th/7fY5SKITwI</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2469,12 +2149,6 @@
           <t>ราคาพิเศษเพียง 199 บาท | ขายได้ 24 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2490,7 +2164,6 @@
           <t>https://s.shopee.co.th/AUsGpXCRHn</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2501,12 +2174,6 @@
           <t>ราคาพิเศษเพียง 233 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2522,7 +2189,6 @@
           <t>https://s.shopee.co.th/AUsGpXLrDC</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2533,12 +2199,6 @@
           <t>ราคาพิเศษเพียง 383 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2554,7 +2214,6 @@
           <t>https://s.shopee.co.th/2BD8uE3XkP</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2565,12 +2224,6 @@
           <t>ราคาพิเศษเพียง 405 บาท | ขายได้ 36 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2586,7 +2239,6 @@
           <t>https://s.shopee.co.th/3ViWUgC0hc</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2597,12 +2249,6 @@
           <t>ราคาพิเศษเพียง 290 บาท | ขายได้ 17 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2618,7 +2264,6 @@
           <t>https://s.shopee.co.th/7AborQ6MzS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2629,12 +2274,6 @@
           <t>ราคาพิเศษเพียง 208 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2650,7 +2289,6 @@
           <t>https://s.shopee.co.th/4AyDHuWMgW</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2661,12 +2299,6 @@
           <t>ราคาพิเศษเพียง 171 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2682,7 +2314,6 @@
           <t>https://s.shopee.co.th/4fuTspglce</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2693,12 +2324,6 @@
           <t>ราคาพิเศษเพียง 510 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2714,7 +2339,6 @@
           <t>https://s.shopee.co.th/9UzjdibQbo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2725,12 +2349,6 @@
           <t>ราคาพิเศษเพียง 97 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2746,7 +2364,6 @@
           <t>https://s.shopee.co.th/2g9PVA9gwT</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2757,12 +2374,6 @@
           <t>ราคาพิเศษเพียง 452 บาท | ขายได้ 239 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2778,7 +2389,6 @@
           <t>https://s.shopee.co.th/80AvqycbsM</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2789,12 +2399,6 @@
           <t>ราคาพิเศษเพียง 363 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2810,7 +2414,6 @@
           <t>https://s.shopee.co.th/3g1wh15cOS</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2821,12 +2424,6 @@
           <t>ราคาพิเศษเพียง 276 บาท | ขายได้ 16 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2842,7 +2439,6 @@
           <t>https://s.shopee.co.th/2VpzIsNfgG</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2853,12 +2449,6 @@
           <t>ราคาพิเศษเพียง 199 บาท | ขายได้ 17 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2874,7 +2464,6 @@
           <t>https://s.shopee.co.th/18eKHkSMZ</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2885,12 +2474,6 @@
           <t>ราคาพิเศษเพียง 49 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2906,7 +2489,6 @@
           <t>https://s.shopee.co.th/9UzjdkOrgx</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2917,12 +2499,6 @@
           <t>ราคาพิเศษเพียง 170 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2938,7 +2514,6 @@
           <t>https://s.shopee.co.th/6L2hrvmTAf</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2949,12 +2524,6 @@
           <t>ราคาพิเศษเพียง 577 บาท | ขายได้ 61 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2970,7 +2539,6 @@
           <t>https://s.shopee.co.th/18eKIO7gN</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2981,12 +2549,6 @@
           <t>ราคาพิเศษเพียง 344 บาท | ขายได้ 15 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3002,7 +2564,6 @@
           <t>https://s.shopee.co.th/7AborTBLSP</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3013,12 +2574,6 @@
           <t>ราคาพิเศษเพียง 777 บาท | ขายได้ 7พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3034,7 +2589,6 @@
           <t>https://s.shopee.co.th/4qDu5BX0y0</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3045,12 +2599,6 @@
           <t>ราคาพิเศษเพียง 840 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3066,7 +2614,6 @@
           <t>https://s.shopee.co.th/8AUM3JW52j</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3077,12 +2624,6 @@
           <t>ราคาพิเศษเพียง 714 บาท | ขายได้ 5 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3098,7 +2639,6 @@
           <t>https://s.shopee.co.th/9zw0Ege9lQ</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3109,12 +2649,6 @@
           <t>ราคาพิเศษเพียง 65 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3130,7 +2664,6 @@
           <t>https://s.shopee.co.th/5fn14j6PNu</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3141,12 +2674,6 @@
           <t>ราคาพิเศษเพียง 239 บาท | ขายได้ 881 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3162,7 +2689,6 @@
           <t>https://s.shopee.co.th/1BKbiSasOl</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3173,12 +2699,6 @@
           <t>ราคาพิเศษเพียง 295 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3194,7 +2714,6 @@
           <t>https://s.shopee.co.th/9AMtFAFDjS</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3205,12 +2724,6 @@
           <t>ราคาพิเศษเพียง 395 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3226,7 +2739,6 @@
           <t>https://s.shopee.co.th/7VEfG6YDLk</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3237,12 +2749,6 @@
           <t>ราคาพิเศษเพียง 82 บาท | ขายได้ 7 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3258,7 +2764,6 @@
           <t>https://s.shopee.co.th/AAFQR0Wiym</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3269,12 +2774,6 @@
           <t>ราคาพิเศษเพียง 336 บาท | ขายได้ 37 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3290,7 +2789,6 @@
           <t>https://s.shopee.co.th/6L2hrxz8Sx</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3301,12 +2799,6 @@
           <t>ราคาพิเศษเพียง 289 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3322,7 +2814,6 @@
           <t>https://s.shopee.co.th/9Uzjdn0UBp</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3333,12 +2824,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3354,7 +2839,6 @@
           <t>https://s.shopee.co.th/6VM84HLsHn</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3365,12 +2849,6 @@
           <t>ราคาพิเศษเพียง 297 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3386,7 +2864,6 @@
           <t>https://s.shopee.co.th/LlUiwutrg</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3397,12 +2874,6 @@
           <t>ราคาพิเศษเพียง 47 บาท | ขายได้ 944 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3418,7 +2889,6 @@
           <t>https://s.shopee.co.th/4LHdUJNSmG</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3429,12 +2899,6 @@
           <t>ราคาพิเศษเพียง 215 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3450,7 +2914,6 @@
           <t>https://s.shopee.co.th/20tii1jc7S</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3461,12 +2924,6 @@
           <t>ราคาพิเศษเพียง 504 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3482,7 +2939,6 @@
           <t>https://s.shopee.co.th/8pk2qaXHRu</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3493,12 +2949,6 @@
           <t>ราคาพิเศษเพียง 75 บาท | ขายได้ 14 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3514,7 +2964,6 @@
           <t>https://s.shopee.co.th/18eKMJ07G</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3525,12 +2974,6 @@
           <t>ราคาพิเศษเพียง 292 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3546,7 +2989,6 @@
           <t>https://s.shopee.co.th/AUsGpen4VE</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3557,12 +2999,6 @@
           <t>ราคาพิเศษเพียง 441 บาท | ขายได้ 312 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3578,7 +3014,6 @@
           <t>https://s.shopee.co.th/3LP6IUMSzy</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3589,12 +3024,6 @@
           <t>ราคาพิเศษเพียง 265 บาท | ขายได้ 18 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3610,7 +3039,6 @@
           <t>https://s.shopee.co.th/6L2hs0KKI1</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3621,12 +3049,6 @@
           <t>ราคาพิเศษเพียง 123 บาท | ขายได้ 13 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3642,7 +3064,6 @@
           <t>https://s.shopee.co.th/80Avr4O9iM</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3653,12 +3074,6 @@
           <t>ราคาพิเศษเพียง 69 บาท | ขายได้ 88 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3674,7 +3089,6 @@
           <t>https://s.shopee.co.th/5VTasTa9F8</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3685,12 +3099,6 @@
           <t>ราคาพิเศษเพียง 1920 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3706,7 +3114,6 @@
           <t>https://s.shopee.co.th/8fQceIXVjD</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3717,12 +3124,6 @@
           <t>ราคาพิเศษเพียง 504 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3738,7 +3139,6 @@
           <t>https://s.shopee.co.th/7prVelivtr</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3749,12 +3149,6 @@
           <t>ราคาพิเศษเพียง 59 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3770,7 +3164,6 @@
           <t>https://s.shopee.co.th/30mFtt9zja</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3781,12 +3174,6 @@
           <t>ราคาพิเศษเพียง 326 บาท | ขายได้ 189 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3802,7 +3189,6 @@
           <t>https://s.shopee.co.th/3g1wh7BvQY</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3813,12 +3199,6 @@
           <t>ราคาพิเศษเพียง 66 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3834,7 +3214,6 @@
           <t>https://s.shopee.co.th/5AqkTsF9TH</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3845,12 +3224,6 @@
           <t>ราคาพิเศษเพียง 150 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3866,7 +3239,6 @@
           <t>https://s.shopee.co.th/2BD8uMUpoj</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3877,12 +3249,6 @@
           <t>ราคาพิเศษเพียง 536 บาท | ขายได้ 829 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3898,7 +3264,6 @@
           <t>https://s.shopee.co.th/AAFQR496sz</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3909,12 +3274,6 @@
           <t>ราคาพิเศษเพียง 416 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3930,7 +3289,6 @@
           <t>https://s.shopee.co.th/5AqkTsX5uh</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3941,12 +3299,6 @@
           <t>ราคาพิเศษเพียง 170 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3962,7 +3314,6 @@
           <t>https://s.shopee.co.th/3LP6IVnu89</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3973,12 +3324,6 @@
           <t>ราคาพิเศษเพียง 245 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3994,7 +3339,6 @@
           <t>https://s.shopee.co.th/40en5joK4K</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4005,12 +3349,6 @@
           <t>ราคาพิเศษเพียง 150 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4026,7 +3364,6 @@
           <t>https://s.shopee.co.th/2BD8uN4eS8</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4037,12 +3374,6 @@
           <t>ราคาพิเศษเพียง 1360 บาท | ขายได้ 5 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4058,7 +3389,6 @@
           <t>https://s.shopee.co.th/4fuTsyQCuy</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4069,12 +3399,6 @@
           <t>ราคาพิเศษเพียง 288 บาท | ขายได้ 46 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4090,7 +3414,6 @@
           <t>https://s.shopee.co.th/5AqkTtWU54</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4101,12 +3424,6 @@
           <t>ราคาพิเศษเพียง 276 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4122,7 +3439,6 @@
           <t>https://s.shopee.co.th/3ViWUplu4m</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4133,12 +3449,6 @@
           <t>ราคาพิเศษเพียง 634 บาท | ขายได้ 12 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4154,7 +3464,6 @@
           <t>https://s.shopee.co.th/7AborZbvqc</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4165,12 +3474,6 @@
           <t>ราคาพิเศษเพียง 383 บาท | ขายได้ 7 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4186,7 +3489,6 @@
           <t>https://s.shopee.co.th/6L2hs2t3na</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4197,12 +3499,6 @@
           <t>ราคาพิเศษเพียง 1600 บาท | ขายได้ 7 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4218,7 +3514,6 @@
           <t>https://s.shopee.co.th/9KgJRYuUig</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4229,12 +3524,6 @@
           <t>ราคาพิเศษเพียง 936 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4250,7 +3539,6 @@
           <t>https://s.shopee.co.th/3g1wh9Udp3</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4261,12 +3549,6 @@
           <t>ราคาพิเศษเพียง 903 บาท | ขายได้ 37 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4282,7 +3564,6 @@
           <t>https://s.shopee.co.th/1qaIVmiZ0z</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4293,12 +3574,6 @@
           <t>ราคาพิเศษเพียง 43 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4314,7 +3589,6 @@
           <t>https://s.shopee.co.th/3ViWUqppYR</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4325,12 +3599,6 @@
           <t>ราคาพิเศษเพียง 427 บาท | ขายได้ 157 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4346,7 +3614,6 @@
           <t>https://s.shopee.co.th/4fuTszzcT5</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4357,12 +3624,6 @@
           <t>ราคาพิเศษเพียง 49 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4378,7 +3639,6 @@
           <t>https://s.shopee.co.th/9fJ9qBnnrE</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4389,12 +3649,6 @@
           <t>ราคาพิเศษเพียง 69 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4410,7 +3664,6 @@
           <t>https://s.shopee.co.th/8KnmFk6hHc</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4421,12 +3674,6 @@
           <t>ราคาพิเศษเพียง 25 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4442,7 +3689,6 @@
           <t>https://s.shopee.co.th/4qDu5JXZ2c</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4453,12 +3699,6 @@
           <t>ราคาพิเศษเพียง 336 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4474,7 +3714,6 @@
           <t>https://s.shopee.co.th/60PrTScXaU</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4485,12 +3724,6 @@
           <t>ราคาพิเศษเพียง 180 บาท | ขายได้ 26 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4506,7 +3739,6 @@
           <t>https://s.shopee.co.th/6VM84NmSg0</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4517,12 +3749,6 @@
           <t>ราคาพิเศษเพียง 382 บาท | ขายได้ 7 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4538,7 +3764,6 @@
           <t>https://s.shopee.co.th/9fJ9qCkzez</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4549,12 +3774,6 @@
           <t>ราคาพิเศษเพียง 383 บาท | ขายได้ 177 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4570,7 +3789,6 @@
           <t>https://s.shopee.co.th/6L2hs58xPs</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4581,12 +3799,6 @@
           <t>ราคาพิเศษเพียง 298 บาท | ขายได้ 19 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4602,7 +3814,6 @@
           <t>https://s.shopee.co.th/8pk2qgE9Rg</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4613,12 +3824,6 @@
           <t>ราคาพิเศษเพียง 675 บาท | ขายได้ 5 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4634,7 +3839,6 @@
           <t>https://s.shopee.co.th/2g9PVLpEtN</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4645,12 +3849,6 @@
           <t>ราคาพิเศษเพียง 69 บาท | ขายได้ 8 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4666,7 +3864,6 @@
           <t>https://s.shopee.co.th/1BKbhWFl4X</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4677,12 +3874,6 @@
           <t>ราคาพิเศษเพียง 27 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4698,7 +3889,6 @@
           <t>https://s.shopee.co.th/3g1wg7FaeC</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4709,12 +3899,6 @@
           <t>ราคาพิเศษเพียง 96 บาท | ขายได้ 6พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4730,7 +3914,6 @@
           <t>https://s.shopee.co.th/BS4VgbEUZ</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4741,12 +3924,6 @@
           <t>ราคาพิเศษเพียง 5 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4762,7 +3939,6 @@
           <t>https://s.shopee.co.th/50XKGZSFb2</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4773,12 +3949,6 @@
           <t>ราคาพิเศษเพียง 13 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4794,7 +3964,6 @@
           <t>https://s.shopee.co.th/7AboqYTyDv</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4805,12 +3974,6 @@
           <t>ราคาพิเศษเพียง 25 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4826,7 +3989,6 @@
           <t>https://s.shopee.co.th/9pca1SVZeY</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4837,12 +3999,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4858,7 +4014,6 @@
           <t>https://s.shopee.co.th/3g1wg8BgFC</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4869,12 +4024,6 @@
           <t>ราคาพิเศษเพียง 15 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4890,7 +4039,6 @@
           <t>https://s.shopee.co.th/40en4kQQez</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4901,12 +4049,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4922,7 +4064,6 @@
           <t>https://s.shopee.co.th/5VTarVcSGK</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4933,12 +4074,6 @@
           <t>ราคาพิเศษเพียง 13 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4954,7 +4089,6 @@
           <t>https://s.shopee.co.th/7prVdnlExh</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4965,12 +4099,6 @@
           <t>ราคาพิเศษเพียง 6 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4986,7 +4114,6 @@
           <t>https://s.shopee.co.th/7VEfFC3yDF</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4997,12 +4124,6 @@
           <t>ราคาพิเศษเพียง 26 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5018,7 +4139,6 @@
           <t>https://s.shopee.co.th/6VM83MPNMl</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5029,12 +4149,6 @@
           <t>ราคาพิเศษเพียง 66 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5050,7 +4164,6 @@
           <t>https://s.shopee.co.th/2LWZ5hsv02</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5061,12 +4174,6 @@
           <t>ราคาพิเศษเพียง 204 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5082,7 +4189,6 @@
           <t>https://s.shopee.co.th/2BD8tPAwgQ</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5093,12 +4199,6 @@
           <t>ราคาพิเศษเพียง 174 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5114,7 +4214,6 @@
           <t>https://s.shopee.co.th/5q6RG9En9w</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5125,12 +4224,6 @@
           <t>ราคาพิเศษเพียง 788 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5146,7 +4239,6 @@
           <t>https://s.shopee.co.th/4qDu4JaGa6</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5157,12 +4249,6 @@
           <t>ราคาพิเศษเพียง 99 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5178,7 +4264,6 @@
           <t>https://s.shopee.co.th/9pca1VZAtx</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5189,12 +4274,6 @@
           <t>ราคาพิเศษเพียง 205 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5210,7 +4289,6 @@
           <t>https://s.shopee.co.th/1VxS6CHCkA</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5221,12 +4299,6 @@
           <t>ราคาพิเศษเพียง 184 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5242,7 +4314,6 @@
           <t>https://s.shopee.co.th/8pk2pg4PXC</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5253,12 +4324,6 @@
           <t>ราคาพิเศษเพียง 69 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5274,7 +4339,6 @@
           <t>https://s.shopee.co.th/7prVdqOVjk</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5285,12 +4349,6 @@
           <t>ราคาพิเศษเพียง 25 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5306,7 +4364,6 @@
           <t>https://s.shopee.co.th/60PrSUHkWD</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5317,12 +4374,6 @@
           <t>ราคาพิเศษเพียง 7 บาท | ขายได้ 4พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5338,7 +4389,6 @@
           <t>https://s.shopee.co.th/18eJSxDmH</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5349,12 +4399,6 @@
           <t>ราคาพิเศษเพียง 25 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5370,7 +4414,6 @@
           <t>https://s.shopee.co.th/6ffYFioThF</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5381,12 +4424,6 @@
           <t>ราคาพิเศษเพียง 7 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5402,7 +4439,6 @@
           <t>https://s.shopee.co.th/80AvqB1xnA</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5413,12 +4449,6 @@
           <t>ราคาพิเศษเพียง 225 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5434,7 +4464,6 @@
           <t>https://s.shopee.co.th/5q6RGCSDsU</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5445,12 +4474,6 @@
           <t>ราคาพิเศษเพียง 12 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5466,7 +4489,6 @@
           <t>https://s.shopee.co.th/7VEfFGc6Nl</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5477,12 +4499,6 @@
           <t>ราคาพิเศษเพียง 119 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5498,7 +4514,6 @@
           <t>https://s.shopee.co.th/40en4q2YZI</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5509,12 +4524,6 @@
           <t>ราคาพิเศษเพียง 64 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5530,7 +4539,6 @@
           <t>https://s.shopee.co.th/8AUM2UzLOt</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5541,12 +4549,6 @@
           <t>ราคาพิเศษเพียง 284 บาท | ขายได้ 981 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5562,7 +4564,6 @@
           <t>https://s.shopee.co.th/7VEfFHL3sV</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5573,12 +4574,6 @@
           <t>ราคาพิเศษเพียง 149 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5594,7 +4589,6 @@
           <t>https://s.shopee.co.th/8KnmEoUKef</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5605,12 +4599,6 @@
           <t>ราคาพิเศษเพียง 154 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5626,7 +4614,6 @@
           <t>https://s.shopee.co.th/2BD8tU4jTW</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5637,12 +4624,6 @@
           <t>ราคาพิเศษเพียง 54 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5658,7 +4639,6 @@
           <t>https://s.shopee.co.th/4fuTs5D5ZL</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5669,12 +4649,6 @@
           <t>ราคาพิเศษเพียง 109 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5690,7 +4664,6 @@
           <t>https://s.shopee.co.th/9KgJQfD3lX</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5701,12 +4674,6 @@
           <t>ราคาพิเศษเพียง 6 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5722,7 +4689,6 @@
           <t>https://s.shopee.co.th/gOL6jxFhW</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5733,12 +4699,6 @@
           <t>ราคาพิเศษเพียง 129 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5754,7 +4714,6 @@
           <t>https://s.shopee.co.th/9KgJQfhrEY</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5765,12 +4724,6 @@
           <t>ราคาพิเศษเพียง 3 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5786,7 +4739,6 @@
           <t>https://s.shopee.co.th/40en4sGOKp</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5797,12 +4749,6 @@
           <t>ราคาพิเศษเพียง 119 บาท | ขายได้ 965 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5818,7 +4764,6 @@
           <t>https://s.shopee.co.th/2qSpgjc1G6</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5829,12 +4774,6 @@
           <t>ราคาพิเศษเพียง 29 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5850,7 +4789,6 @@
           <t>https://s.shopee.co.th/9fJ9pISqdb</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5861,12 +4799,6 @@
           <t>ราคาพิเศษเพียง 295 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5882,7 +4814,6 @@
           <t>https://s.shopee.co.th/4LHdTV4c5m</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5893,12 +4824,6 @@
           <t>ราคาพิเศษเพียง 15 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5914,7 +4839,6 @@
           <t>https://s.shopee.co.th/8pk2pm4Wy8</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5925,12 +4849,6 @@
           <t>ราคาพิเศษเพียง 206 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5946,7 +4864,6 @@
           <t>https://s.shopee.co.th/8fQcdTwmqO</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5957,12 +4874,6 @@
           <t>ราคาพิเศษเพียง 65 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5978,7 +4889,6 @@
           <t>https://s.shopee.co.th/6VM83VLfhL</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5989,12 +4899,6 @@
           <t>ราคาพิเศษเพียง 76 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6010,7 +4914,6 @@
           <t>https://s.shopee.co.th/3qLMsbo2b9</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6021,12 +4924,6 @@
           <t>ราคาพิเศษเพียง 198 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6042,7 +4939,6 @@
           <t>https://s.shopee.co.th/2BD8tYCKR4</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6053,12 +4949,6 @@
           <t>ราคาพิเศษเพียง 110 บาท | ขายได้ 20พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6074,7 +4964,6 @@
           <t>https://s.shopee.co.th/20tihFYLJP</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6085,12 +4974,6 @@
           <t>ราคาพิเศษเพียง 154 บาท | ขายได้ 886 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6106,7 +4989,6 @@
           <t>https://s.shopee.co.th/60PrSbaVXX</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6117,12 +4999,6 @@
           <t>ราคาพิเศษเพียง 28 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6138,7 +5014,6 @@
           <t>https://s.shopee.co.th/2qSpgn41bw</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6149,12 +5024,6 @@
           <t>ราคาพิเศษเพียง 34 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6170,7 +5039,6 @@
           <t>https://s.shopee.co.th/4fuTsAAaVe</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6181,12 +5049,6 @@
           <t>ราคาพิเศษเพียง 158 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6202,7 +5064,6 @@
           <t>https://s.shopee.co.th/2qSpgnYtJH</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6213,12 +5074,6 @@
           <t>ราคาพิเศษเพียง 50 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6234,7 +5089,6 @@
           <t>https://s.shopee.co.th/8fQcdWUHbe</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6245,12 +5099,6 @@
           <t>ราคาพิเศษเพียง 33 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6266,7 +5114,6 @@
           <t>https://s.shopee.co.th/6VM83Xubyn</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6277,12 +5124,6 @@
           <t>ราคาพิเศษเพียง 68 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6298,7 +5139,6 @@
           <t>https://s.shopee.co.th/903T292h1r</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6309,12 +5149,6 @@
           <t>ราคาพิเศษเพียง 10 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6330,7 +5164,6 @@
           <t>https://s.shopee.co.th/5fn141SrBX</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6341,12 +5174,6 @@
           <t>ราคาพิเศษเพียง 88 บาท | ขายได้ 394 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6362,7 +5189,6 @@
           <t>https://s.shopee.co.th/6ffYFrhokq</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6373,12 +5199,6 @@
           <t>ราคาพิเศษเพียง 65 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -6394,7 +5214,6 @@
           <t>https://s.shopee.co.th/9fJ9pNm0BD</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6405,12 +5224,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6426,7 +5239,6 @@
           <t>https://s.shopee.co.th/4LHdTaOFRa</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6437,12 +5249,6 @@
           <t>ราคาพิเศษเพียง 209 บาท | ขายได้ 926 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6458,7 +5264,6 @@
           <t>https://s.shopee.co.th/9pca1hLBSl</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6469,12 +5274,6 @@
           <t>ราคาพิเศษเพียง 9 บาท | ขายได้ 810 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6490,7 +5289,6 @@
           <t>https://s.shopee.co.th/8pk2prgJaW</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6501,12 +5299,6 @@
           <t>ราคาพิเศษเพียง 151 บาท | ขายได้ 848 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6522,7 +5314,6 @@
           <t>https://s.shopee.co.th/AKYqccp2br</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6533,12 +5324,6 @@
           <t>ราคาพิเศษเพียง 204 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6554,7 +5339,6 @@
           <t>https://s.shopee.co.th/9fJ9pP7fJG</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6565,12 +5349,6 @@
           <t>ราคาพิเศษเพียง 82 บาท | ขายได้ 929 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6586,7 +5364,6 @@
           <t>https://s.shopee.co.th/3ViWU5MDIq</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6597,12 +5374,6 @@
           <t>ราคาพิเศษเพียง 159 บาท | ขายได้ 872 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6618,7 +5389,6 @@
           <t>https://s.shopee.co.th/AKYqceDWTl</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6629,12 +5399,6 @@
           <t>ราคาพิเศษเพียง 169 บาท | ขายได้ 916 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6650,7 +5414,6 @@
           <t>https://s.shopee.co.th/2qSpgrzbCy</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6661,12 +5424,6 @@
           <t>ราคาพิเศษเพียง 58 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6682,7 +5439,6 @@
           <t>https://s.shopee.co.th/AKYqceiwJg</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6693,12 +5449,6 @@
           <t>ราคาพิเศษเพียง 204 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6714,7 +5464,6 @@
           <t>https://s.shopee.co.th/111BVVZvrQ</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6725,12 +5474,6 @@
           <t>ราคาพิเศษเพียง 60 บาท | ขายได้ 939 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6746,7 +5489,6 @@
           <t>https://s.shopee.co.th/7prVe4MuYP</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6757,12 +5499,6 @@
           <t>ราคาพิเศษเพียง 198 บาท | ขายได้ 929 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6778,7 +5514,6 @@
           <t>https://s.shopee.co.th/BS4Vz2x96</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6789,12 +5524,6 @@
           <t>ราคาพิเศษเพียง 85 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6810,7 +5539,6 @@
           <t>https://s.shopee.co.th/6VM83cjvha</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6821,12 +5549,6 @@
           <t>ราคาพิเศษเพียง 6 บาท | ขายได้ 20พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6842,7 +5564,6 @@
           <t>https://s.shopee.co.th/9AMtEWns3u</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6853,12 +5574,6 @@
           <t>ราคาพิเศษเพียง 165 บาท | ขายได้ 884 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6874,7 +5589,6 @@
           <t>https://s.shopee.co.th/3ViWU7PfSD</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6885,12 +5599,6 @@
           <t>ราคาพิเศษเพียง 5 บาท | ขายได้ 890 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6906,7 +5614,6 @@
           <t>https://s.shopee.co.th/3LP6Hoe7Td</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6917,12 +5624,6 @@
           <t>ราคาพิเศษเพียง 898 บาท | ขายได้ 882 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6938,7 +5639,6 @@
           <t>https://s.shopee.co.th/40en52odwn</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6949,12 +5649,6 @@
           <t>ราคาพิเศษเพียง 24 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6970,7 +5664,6 @@
           <t>https://s.shopee.co.th/7prVe5nBFn</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6981,12 +5674,6 @@
           <t>ราคาพิเศษเพียง 40 บาท | ขายได้ 759 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7002,7 +5689,6 @@
           <t>https://s.shopee.co.th/9pca1ly7zu</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7013,12 +5699,6 @@
           <t>ราคาพิเศษเพียง 107 บาท | ขายได้ 762 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7034,7 +5714,6 @@
           <t>https://s.shopee.co.th/AAFQQO91kT</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7045,12 +5724,6 @@
           <t>ราคาพิเศษเพียง 132 บาท | ขายได้ 2พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7066,7 +5739,6 @@
           <t>https://s.shopee.co.th/9pca1mVskZ</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7077,12 +5749,6 @@
           <t>ราคาพิเศษเพียง 88 บาท | ขายได้ 598 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7098,7 +5764,6 @@
           <t>https://s.shopee.co.th/8fQcddrvGJ</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7109,12 +5774,6 @@
           <t>ราคาพิเศษเพียง 510 บาท | ขายได้ 728 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7130,7 +5789,6 @@
           <t>https://s.shopee.co.th/4Vb3fzQpMi</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7141,12 +5799,6 @@
           <t>ราคาพิเศษเพียง 278 บาท | ขายได้ 853 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -7162,7 +5814,6 @@
           <t>https://s.shopee.co.th/5LAAfWedQp</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7173,12 +5824,6 @@
           <t>ราคาพิเศษเพียง 39 บาท | ขายได้ 848 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -7194,7 +5839,6 @@
           <t>https://s.shopee.co.th/LlUiLGId2</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7205,12 +5849,6 @@
           <t>ราคาพิเศษเพียง 52 บาท | ขายได้ 891 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -7226,7 +5864,6 @@
           <t>https://s.shopee.co.th/4AyDHOmw07</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7237,12 +5874,6 @@
           <t>ราคาพิเศษเพียง 157 บาท | ขายได้ 744 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -7258,7 +5889,6 @@
           <t>https://s.shopee.co.th/7prVe8rKaS</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7269,12 +5899,6 @@
           <t>ราคาพิเศษเพียง 274 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -7290,7 +5914,6 @@
           <t>https://s.shopee.co.th/60PrSmEwkn</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7301,12 +5924,6 @@
           <t>ราคาพิเศษเพียง 13 บาท | ขายได้ 785 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -7322,7 +5939,6 @@
           <t>https://s.shopee.co.th/2qSpgxdvUb</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7333,12 +5949,6 @@
           <t>ราคาพิเศษเพียง 49 บาท | ขายได้ 404 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -7354,7 +5964,6 @@
           <t>https://s.shopee.co.th/3ViWUBppDY</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7365,12 +5974,6 @@
           <t>ราคาพิเศษเพียง 144 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -7386,7 +5989,6 @@
           <t>https://s.shopee.co.th/18eJlLA00</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7397,12 +5999,6 @@
           <t>ราคาพิเศษเพียง 20 บาท | ขายได้ 4พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -7418,7 +6014,6 @@
           <t>https://s.shopee.co.th/70IOed6gEM</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7429,12 +6024,6 @@
           <t>ราคาพิเศษเพียง 236 บาท | ขายได้ 830 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -7450,7 +6039,6 @@
           <t>https://s.shopee.co.th/gOL6zn0ZU</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7461,12 +6049,6 @@
           <t>ราคาพิเศษเพียง 39 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7482,7 +6064,6 @@
           <t>https://s.shopee.co.th/8KnmF5aSS6</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7493,12 +6074,6 @@
           <t>ราคาพิเศษเพียง 284 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7514,7 +6089,6 @@
           <t>https://s.shopee.co.th/9fJ9pXn39G</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7525,12 +6099,6 @@
           <t>ราคาพิเศษเพียง 155 บาท | ขายได้ 684 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7546,7 +6114,6 @@
           <t>https://s.shopee.co.th/2BD8tlSwED</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7557,12 +6124,6 @@
           <t>ราคาพิเศษเพียง 37 บาท | ขายได้ 9พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7578,7 +6139,6 @@
           <t>https://s.shopee.co.th/AAFQQTAzin</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7589,12 +6149,6 @@
           <t>ราคาพิเศษเพียง 64 บาท | ขายได้ 10พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7610,7 +6164,6 @@
           <t>https://s.shopee.co.th/3qLMspmr2A</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7621,12 +6174,6 @@
           <t>ราคาพิเศษเพียง 28 บาท | ขายได้ 853 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7642,7 +6189,6 @@
           <t>https://s.shopee.co.th/18eJnJ2vU</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7653,12 +6199,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 791 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7674,7 +6214,6 @@
           <t>https://s.shopee.co.th/5q6RGWDt8R</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7685,12 +6224,6 @@
           <t>ราคาพิเศษเพียง 154 บาท | ขายได้ 1พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7706,7 +6239,6 @@
           <t>https://s.shopee.co.th/9zw0EBFUHg</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7717,12 +6249,6 @@
           <t>ราคาพิเศษเพียง 9 บาท | ขายได้ 970 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7738,7 +6264,6 @@
           <t>https://s.shopee.co.th/5fn14DklSQ</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7749,12 +6274,6 @@
           <t>ราคาพิเศษเพียง 225 บาท | ขายได้ 6พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7770,7 +6289,6 @@
           <t>https://s.shopee.co.th/903T2LoA2l</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7781,12 +6299,6 @@
           <t>ราคาพิเศษเพียง 240 บาท | ขายได้ 3พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7802,7 +6314,6 @@
           <t>https://s.shopee.co.th/5fn14EIaUA</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7813,12 +6324,6 @@
           <t>ราคาพิเศษเพียง 37 บาท | ขายได้ 715 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7834,7 +6339,6 @@
           <t>https://s.shopee.co.th/AUsGp7HeGo</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7845,12 +6349,6 @@
           <t>ราคาพิเศษเพียง 47 บาท | ขายได้ 4พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7866,7 +6364,6 @@
           <t>https://s.shopee.co.th/1VxS7D5qgi</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7877,12 +6374,6 @@
           <t>ราคาพิเศษเพียง 75 บาท | ขายได้ 4พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7898,7 +6389,6 @@
           <t>https://s.shopee.co.th/80AvrF15AH</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7909,12 +6399,6 @@
           <t>ราคาพิเศษเพียง 4 บาท | ขายได้ 310 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7930,7 +6414,6 @@
           <t>https://s.shopee.co.th/6AjHfsCBcG</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7941,12 +6424,6 @@
           <t>ราคาพิเศษเพียง 10 บาท | ขายได้ 60 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7962,7 +6439,6 @@
           <t>https://s.shopee.co.th/AKYqdX4Zec</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7973,12 +6449,6 @@
           <t>ราคาพิเศษเพียง 103 บาท | ขายได้ 202 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7994,7 +6464,6 @@
           <t>https://s.shopee.co.th/80AvrFRLKb</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8005,12 +6474,6 @@
           <t>ราคาพิเศษเพียง 400 บาท | ขายได้ 36 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -8026,7 +6489,6 @@
           <t>https://s.shopee.co.th/1gGsJc2RlS</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8037,12 +6499,6 @@
           <t>ราคาพิเศษเพียง 89 บาท | ขายได้ 31 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -8058,7 +6514,6 @@
           <t>https://s.shopee.co.th/60PrTZyWw9</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8069,12 +6524,6 @@
           <t>ราคาพิเศษเพียง 67 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8090,7 +6539,6 @@
           <t>https://s.shopee.co.th/4AyDIDJfgl</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8101,12 +6549,6 @@
           <t>ราคาพิเศษเพียง 88 บาท | ขายได้ 61 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8122,7 +6564,6 @@
           <t>https://s.shopee.co.th/9fJ9qKBaYO</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8133,12 +6574,6 @@
           <t>ราคาพิเศษเพียง 500 บาท | ขายได้ 22 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -8154,7 +6589,6 @@
           <t>https://s.shopee.co.th/3B5g6NkVbz</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8165,12 +6599,6 @@
           <t>ราคาพิเศษเพียง 188 บาท | ขายได้ 403 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -8186,7 +6614,6 @@
           <t>https://s.shopee.co.th/7fY5SeevTQ</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8197,12 +6624,6 @@
           <t>ราคาพิเศษเพียง 89 บาท | ขายได้ 23 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -8218,7 +6639,6 @@
           <t>https://s.shopee.co.th/8KnmFspF9s</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8229,12 +6649,6 @@
           <t>ราคาพิเศษเพียง 57 บาท | ขายได้ 7พัน+ ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -8250,7 +6664,6 @@
           <t>https://s.shopee.co.th/AAFQRFvo6B</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8261,12 +6674,6 @@
           <t>ราคาพิเศษเพียง 91 บาท | ขายได้ 16 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -8282,7 +6689,6 @@
           <t>https://s.shopee.co.th/6VM84WOCbh</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8293,12 +6699,6 @@
           <t>ราคาพิเศษเพียง 593 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -8314,7 +6714,6 @@
           <t>https://s.shopee.co.th/4fuTt9h8x5</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8325,12 +6724,6 @@
           <t>ราคาพิเศษเพียง 99 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -8346,7 +6739,6 @@
           <t>https://s.shopee.co.th/8KnmFtgrhB</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8357,12 +6749,6 @@
           <t>ราคาพิเศษเพียง 179 บาท | ขายได้ 14 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -8378,7 +6764,6 @@
           <t>https://s.shopee.co.th/2VpzJBFRlB</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8389,12 +6774,6 @@
           <t>ราคาพิเศษเพียง 160 บาท | ขายได้ 10 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -8410,7 +6789,6 @@
           <t>https://s.shopee.co.th/50XKHmL7f1</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8421,12 +6799,6 @@
           <t>ราคาพิเศษเพียง 88 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8442,7 +6814,6 @@
           <t>https://s.shopee.co.th/AAFQRH9q9C</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8453,12 +6824,6 @@
           <t>ราคาพิเศษเพียง 105 บาท | ขายได้ 70 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -8474,7 +6839,6 @@
           <t>https://s.shopee.co.th/9KgJRkOpwT</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8485,12 +6849,6 @@
           <t>ราคาพิเศษเพียง 75 บาท | ขายได้ 178 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8506,7 +6864,6 @@
           <t>https://s.shopee.co.th/1gGsJf5qBy</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8517,12 +6874,6 @@
           <t>ราคาพิเศษเพียง 1425 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8538,7 +6889,6 @@
           <t>https://s.shopee.co.th/AKYqdbKcqx</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8549,12 +6899,6 @@
           <t>ราคาพิเศษเพียง 150 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8570,7 +6914,6 @@
           <t>https://s.shopee.co.th/4qDu5UscpA</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8581,12 +6924,6 @@
           <t>ราคาพิเศษเพียง 159 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8602,7 +6939,6 @@
           <t>https://s.shopee.co.th/1qaIVzHJWM</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8613,12 +6949,6 @@
           <t>ราคาพิเศษเพียง 514 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8634,7 +6964,6 @@
           <t>https://s.shopee.co.th/BS4WvciKX</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8645,12 +6974,6 @@
           <t>ราคาพิเศษเพียง 49 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8666,7 +6989,6 @@
           <t>https://s.shopee.co.th/18eKcpF29</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8677,12 +6999,6 @@
           <t>ราคาพิเศษเพียง 50 บาท | ขายได้ 6 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8698,7 +7014,6 @@
           <t>https://s.shopee.co.th/5AqkU7idNK</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8709,12 +7024,6 @@
           <t>ราคาพิเศษเพียง 96 บาท | ขายได้ 7 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8730,7 +7039,6 @@
           <t>https://s.shopee.co.th/gOL7rCcXa</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8741,12 +7049,6 @@
           <t>ราคาพิเศษเพียง 600 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8762,7 +7064,6 @@
           <t>https://s.shopee.co.th/5AqkU89AcS</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8773,12 +7074,6 @@
           <t>ราคาพิเศษเพียง 149 บาท | ขายได้ 3 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8794,7 +7089,6 @@
           <t>https://s.shopee.co.th/5AqkU8Qlij</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8805,12 +7099,6 @@
           <t>ราคาพิเศษเพียง 4500 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8826,7 +7114,6 @@
           <t>https://s.shopee.co.th/2LWZ6vkd5M</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8837,12 +7124,6 @@
           <t>ราคาพิเศษเพียง 1498 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8858,7 +7139,6 @@
           <t>https://s.shopee.co.th/40en5zqrhW</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8869,12 +7149,6 @@
           <t>ราคาพิเศษเพียง 111 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8890,7 +7164,6 @@
           <t>https://s.shopee.co.th/7KvF47rr6x</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8901,12 +7174,6 @@
           <t>ราคาพิเศษเพียง 119 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8922,7 +7189,6 @@
           <t>https://s.shopee.co.th/7prVf339Rs</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8933,12 +7199,6 @@
           <t>ราคาพิเศษเพียง 13 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8954,7 +7214,6 @@
           <t>https://s.shopee.co.th/BS4Wxj3Y0</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8965,12 +7224,6 @@
           <t>ราคาพิเศษเพียง 110 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8986,7 +7239,6 @@
           <t>https://s.shopee.co.th/2BD8udp7dW</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8997,12 +7249,6 @@
           <t>ราคาพิเศษเพียง 250 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -9018,7 +7264,6 @@
           <t>https://s.shopee.co.th/AKYqdeWc3R</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9029,12 +7274,6 @@
           <t>ราคาพิเศษเพียง 34 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -9050,7 +7289,6 @@
           <t>https://s.shopee.co.th/70IOfWsVyq</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9061,12 +7299,6 @@
           <t>ราคาพิเศษเพียง 89 บาท | ขายได้ 2 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -9082,7 +7314,6 @@
           <t>https://s.shopee.co.th/8KnmFz01FW</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9093,12 +7324,6 @@
           <t>ราคาพิเศษเพียง 323 บาท | ขายได้ 9 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -9114,7 +7339,6 @@
           <t>https://s.shopee.co.th/W4uvahaah</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9125,12 +7349,6 @@
           <t>ราคาพิเศษเพียง 59 บาท | ขายได้ 3 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -9146,7 +7364,6 @@
           <t>https://s.shopee.co.th/5LAAfiMAyZ</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9157,12 +7374,6 @@
           <t>ราคาพิเศษเพียง 100 บาท | ขายได้ 18 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -9178,7 +7389,6 @@
           <t>https://s.shopee.co.th/111BVkrJbg</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9189,12 +7399,6 @@
           <t>ราคาพิเศษเพียง 182 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -9210,7 +7414,6 @@
           <t>https://s.shopee.co.th/gOL790Lut</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9221,12 +7424,6 @@
           <t>ราคาพิเศษเพียง 202 บาท | ขายได้ 2 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -9242,7 +7439,6 @@
           <t>https://s.shopee.co.th/111BVl7blo</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9253,12 +7449,6 @@
           <t>ราคาพิเศษเพียง 34 บาท | ขายได้ 4 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -9274,7 +7464,6 @@
           <t>https://s.shopee.co.th/3g1wgf6WxV</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9285,12 +7474,6 @@
           <t>ราคาพิเศษเพียง 155 บาท | ขายได้ 2 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -9306,7 +7489,6 @@
           <t>https://s.shopee.co.th/5AqkTQD7rt</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9317,12 +7499,6 @@
           <t>ราคาพิเศษเพียง 386 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -9338,7 +7514,6 @@
           <t>https://s.shopee.co.th/gOL79hSKd</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9349,12 +7524,6 @@
           <t>ราคาพิเศษเพียง 1681 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -9370,7 +7539,6 @@
           <t>https://s.shopee.co.th/60PrSxVx5L</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9381,12 +7549,6 @@
           <t>ราคาพิเศษเพียง 214 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -9402,7 +7564,6 @@
           <t>https://s.shopee.co.th/1BKbi51Tyt</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9413,12 +7574,6 @@
           <t>ราคาพิเศษเพียง 109 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9434,7 +7589,6 @@
           <t>https://s.shopee.co.th/W4uurLpFb</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9445,12 +7599,6 @@
           <t>ราคาพิเศษเพียง 162 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -9466,7 +7614,6 @@
           <t>https://s.shopee.co.th/80AvqeBd2K</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9477,12 +7624,6 @@
           <t>ราคาพิเศษเพียง 147 บาท | ขายได้ 3 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -9498,7 +7639,6 @@
           <t>https://s.shopee.co.th/6L2hraUpS6</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9509,12 +7649,6 @@
           <t>ราคาพิเศษเพียง 806 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -9530,7 +7664,6 @@
           <t>https://s.shopee.co.th/1Le1uP5fVx</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9541,12 +7674,6 @@
           <t>ราคาพิเศษเพียง 52 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9562,7 +7689,6 @@
           <t>https://s.shopee.co.th/5q6RGg5W9m</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9573,12 +7699,6 @@
           <t>ราคาพิเศษเพียง 644 บาท | ขายได้ 11 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9594,7 +7714,6 @@
           <t>https://s.shopee.co.th/9KgJR76ldw</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9605,12 +7724,6 @@
           <t>ราคาพิเศษเพียง 499 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9626,7 +7739,6 @@
           <t>https://s.shopee.co.th/20tihdkvDF</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9637,12 +7749,6 @@
           <t>ราคาพิเศษเพียง 2088 บาท</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9658,7 +7764,6 @@
           <t>https://s.shopee.co.th/7fY5S3gwpf</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9669,12 +7774,6 @@
           <t>ราคาพิเศษเพียง 510 บาท</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9690,7 +7789,6 @@
           <t>https://s.shopee.co.th/3B5g5nBHJB</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9701,12 +7799,6 @@
           <t>ราคาพิเศษเพียง 542 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9722,7 +7814,6 @@
           <t>https://s.shopee.co.th/AKYqcxsWHc</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9733,12 +7824,6 @@
           <t>ราคาพิเศษเพียง 510 บาท</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9754,7 +7839,6 @@
           <t>https://s.shopee.co.th/1VxS6jZ9Yl</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9765,12 +7849,6 @@
           <t>ราคาพิเศษเพียง 124 บาท</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9786,7 +7864,6 @@
           <t>https://s.shopee.co.th/6ffYGEokbC</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9797,12 +7874,6 @@
           <t>ราคาพิเศษเพียง 172 บาท</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9818,7 +7889,6 @@
           <t>https://s.shopee.co.th/2BD8tyE3wo</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9829,12 +7899,6 @@
           <t>ราคาพิเศษเพียง 153 บาท</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9850,7 +7914,6 @@
           <t>https://s.shopee.co.th/9UzjdRvdFe</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9861,12 +7924,6 @@
           <t>ราคาพิเศษเพียง 178 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9882,7 +7939,6 @@
           <t>https://s.shopee.co.th/20tihfWqV9</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9893,12 +7949,6 @@
           <t>ราคาพิเศษเพียง 1937 บาท</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9914,7 +7964,6 @@
           <t>https://s.shopee.co.th/3g1wgjZZjV</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9925,12 +7974,6 @@
           <t>ราคาพิเศษเพียง 1446 บาท</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9946,7 +7989,6 @@
           <t>https://s.shopee.co.th/9fJ9plKum9</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9957,12 +7999,6 @@
           <t>ราคาพิเศษเพียง 710 บาท</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9978,7 +8014,6 @@
           <t>https://s.shopee.co.th/8V7CRcd2JM</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9989,12 +8024,6 @@
           <t>ราคาพิเศษเพียง 1931 บาท</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -10010,7 +8039,6 @@
           <t>https://s.shopee.co.th/3ViWUR4OBe</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10021,12 +8049,6 @@
           <t>ราคาพิเศษเพียง 1961 บาท</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -10042,7 +8064,6 @@
           <t>https://s.shopee.co.th/8V7CRculy4</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10053,12 +8074,6 @@
           <t>ราคาพิเศษเพียง 1167 บาท</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -10074,7 +8089,6 @@
           <t>https://s.shopee.co.th/5AqkTVGOp9</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10085,12 +8099,6 @@
           <t>ราคาพิเศษเพียง 251 บาท</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -10106,7 +8114,6 @@
           <t>https://s.shopee.co.th/2g9PUucyiO</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10117,12 +8124,6 @@
           <t>ราคาพิเศษเพียง 1146 บาท</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -10138,7 +8139,6 @@
           <t>https://s.shopee.co.th/BS4WJwSoe</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10149,12 +8149,6 @@
           <t>ราคาพิเศษเพียง 217 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -10170,7 +8164,6 @@
           <t>https://s.shopee.co.th/7prVePfRfX</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10181,12 +8174,6 @@
           <t>ราคาพิเศษเพียง 1274 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -10202,7 +8189,6 @@
           <t>https://s.shopee.co.th/7AborBptBz</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10213,12 +8199,6 @@
           <t>ราคาพิเศษเพียง 59 บาท | ขายได้ 1 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -10234,7 +8214,6 @@
           <t>https://s.shopee.co.th/9UzjdTuxft</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10245,12 +8224,6 @@
           <t>ราคาพิเศษเพียง 49 บาท</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -10266,7 +8239,6 @@
           <t>https://s.shopee.co.th/6ffYGHEgWP</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10277,12 +8249,6 @@
           <t>ราคาพิเศษเพียง 49 บาท | ขายได้ 2 ชิ้นต่อเดือน</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -10298,7 +8264,6 @@
           <t>https://s.shopee.co.th/8pk2qGELGy</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10309,12 +8274,6 @@
           <t>ราคาพิเศษเพียง 203 บาท</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -10330,7 +8289,6 @@
           <t>https://s.shopee.co.th/8AUM32LLfg</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10341,12 +8299,146 @@
           <t>ราคาพิเศษเพียง 269 บาท</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>285</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max ชิป A20 Pro กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store ของแท้ 100% พร้อมรับสิทธิ์ผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>286</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย 1 ปีเต็ม</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>287</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้ ผ่อน 0% ได้</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>288</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island สุดคุ้มค่า ใช้งานลื่นไหลยาวนาน เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L305"/>
+  <dimension ref="A1:L321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8440,6 +8440,646 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>289</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink ราคา 2250.00 บาท</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>290</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet ราคา 4100.00 บาท</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>291</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด ราคา 1319.00 บาท</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>292</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 17/17 Air/17 Pro/17 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pltueeZSk</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 17/17 Air/17 Pro/17 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์ ราคา 690.00 บาท</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me464fn2gzy9c4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>293</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี ราคา 1798.00 บาท</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>294</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Rubber Killer - JOURNEY LOGO T-SHIRT (เสื้อยืดคอกลม)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40ge9qm9Up</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Rubber Killer - JOURNEY LOGO T-SHIRT (เสื้อยืดคอกลม) ราคา 950.00 บาท</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lu0rwfi2o9ht0d.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>295</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน ราคา 4730.00 บาท</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>296</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ ราคา 1955.00 บาท</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>297</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix ราคา 9490.00 บาท</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>298</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า ราคา 875.00 บาท</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>299</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้ ราคา 634.00 บาท</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>300</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 18 Pro/18 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAHHVDfOkK</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 18 Pro/18 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์ ราคา 1250.00 บาท</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-msm7y6m7hs7409.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>301</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 14290.00 บาท</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>302</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control ราคา 1287.00 บาท</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>303</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>🔥พร้อมส่ง🔥 เสื้อ Guns N' Roses Thailand Bankok (2017) Tee - Black (สีดำ) by XSHT</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBJt9y0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>🔥พร้อมส่ง🔥 เสื้อ Guns N' Roses Thailand Bankok (2017) Tee - Black (สีดำ) by XSHT ราคา 595.00 บาท</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-ly6pmx1kzfl554.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>304</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี ราคา 2107.00 บาท</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
